--- a/tests/fixtures/synthetic_od_table.xlsx
+++ b/tests/fixtures/synthetic_od_table.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,12 +1935,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rival Air</t>
+          <t>Rival R1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rival Air</t>
+          <t>Rival R2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2055,12 +2055,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rival Air</t>
+          <t>Rival R3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2115,12 +2115,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rival Air</t>
+          <t>Rival R4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rival Air</t>
+          <t>Rival R4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2194,14 +2194,14 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8005</v>
+        <v>8014</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>46027.41666666666</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2215,20 +2215,80 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>8105</v>
+        <v>8114</v>
       </c>
       <c r="K30" s="1" t="n">
         <v>46027.47916666666</v>
       </c>
       <c r="L30" s="2" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ZZB-ZZA</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rival R5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ZZB</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>XHB</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>8005</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>46027.41666666666</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>XHB</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ZZA</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>8105</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>46027.47916666666</v>
+      </c>
+      <c r="L31" s="2" t="n">
         <v>0.3090277777777778</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>ZZB-ZZA</t>
         </is>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
     </row>
